--- a/artfynd/A 35188-2025 artfynd.xlsx
+++ b/artfynd/A 35188-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127475411</v>
       </c>
       <c r="B2" t="n">
-        <v>98421</v>
+        <v>98425</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -788,7 +788,7 @@
         <v>127475412</v>
       </c>
       <c r="B3" t="n">
-        <v>98360</v>
+        <v>98364</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 35188-2025 artfynd.xlsx
+++ b/artfynd/A 35188-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127475411</v>
       </c>
       <c r="B2" t="n">
-        <v>98425</v>
+        <v>98426</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -788,7 +788,7 @@
         <v>127475412</v>
       </c>
       <c r="B3" t="n">
-        <v>98364</v>
+        <v>98365</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 35188-2025 artfynd.xlsx
+++ b/artfynd/A 35188-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127475411</v>
       </c>
       <c r="B2" t="n">
-        <v>98426</v>
+        <v>98428</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -788,7 +788,7 @@
         <v>127475412</v>
       </c>
       <c r="B3" t="n">
-        <v>98365</v>
+        <v>98367</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 35188-2025 artfynd.xlsx
+++ b/artfynd/A 35188-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127475411</v>
       </c>
       <c r="B2" t="n">
-        <v>98428</v>
+        <v>98434</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -788,7 +788,7 @@
         <v>127475412</v>
       </c>
       <c r="B3" t="n">
-        <v>98367</v>
+        <v>98373</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 35188-2025 artfynd.xlsx
+++ b/artfynd/A 35188-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127475411</v>
       </c>
       <c r="B2" t="n">
-        <v>98434</v>
+        <v>98437</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -788,7 +788,7 @@
         <v>127475412</v>
       </c>
       <c r="B3" t="n">
-        <v>98373</v>
+        <v>98376</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 35188-2025 artfynd.xlsx
+++ b/artfynd/A 35188-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127475411</v>
       </c>
       <c r="B2" t="n">
-        <v>98437</v>
+        <v>98445</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -788,7 +788,7 @@
         <v>127475412</v>
       </c>
       <c r="B3" t="n">
-        <v>98376</v>
+        <v>98384</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 35188-2025 artfynd.xlsx
+++ b/artfynd/A 35188-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127475411</v>
       </c>
       <c r="B2" t="n">
-        <v>98445</v>
+        <v>98446</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -788,7 +788,7 @@
         <v>127475412</v>
       </c>
       <c r="B3" t="n">
-        <v>98384</v>
+        <v>98385</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 35188-2025 artfynd.xlsx
+++ b/artfynd/A 35188-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127475411</v>
       </c>
       <c r="B2" t="n">
-        <v>98446</v>
+        <v>98447</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -788,7 +788,7 @@
         <v>127475412</v>
       </c>
       <c r="B3" t="n">
-        <v>98385</v>
+        <v>98386</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 35188-2025 artfynd.xlsx
+++ b/artfynd/A 35188-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127475411</v>
       </c>
       <c r="B2" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -788,7 +788,7 @@
         <v>127475412</v>
       </c>
       <c r="B3" t="n">
-        <v>98386</v>
+        <v>98387</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 35188-2025 artfynd.xlsx
+++ b/artfynd/A 35188-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127475411</v>
+        <v>127475412</v>
       </c>
       <c r="B2" t="n">
-        <v>98448</v>
+        <v>99035</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,26 +686,26 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>219798</v>
+        <v>219790</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J2" t="inlineStr"/>
@@ -718,7 +718,7 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>637111</v>
+        <v>637110</v>
       </c>
       <c r="R2" t="n">
         <v>6707830</v>
@@ -785,10 +785,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127475412</v>
+        <v>127475411</v>
       </c>
       <c r="B3" t="n">
-        <v>98387</v>
+        <v>99096</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -796,26 +796,26 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>219790</v>
+        <v>219798</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J3" t="inlineStr"/>
@@ -828,7 +828,7 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>637110</v>
+        <v>637111</v>
       </c>
       <c r="R3" t="n">
         <v>6707830</v>
@@ -888,6 +888,217 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>127475408</v>
+      </c>
+      <c r="B4" t="n">
+        <v>108194</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>220103</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Klasefibbla</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Crepis praemorsa</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(L.) Walther</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Karlsäter, Upl</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>637093</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6707913</v>
+      </c>
+      <c r="S4" t="n">
+        <v>5</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Tierp</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Västland</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-05-15</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-05-15</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF4" t="inlineStr"/>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Staffan Fridh</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Johan Kjetselberg</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>127503778</v>
+      </c>
+      <c r="B5" t="n">
+        <v>106156</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>221141</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Gullviva</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Primula veris</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Karlsäter, Upl</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>637059</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6707936</v>
+      </c>
+      <c r="S5" t="n">
+        <v>5</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Tierp</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Västland</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-05-15</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-05-15</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Staffan Fridh</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Tore Dahlberg</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
         <is>
           <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
         </is>

--- a/artfynd/A 35188-2025 artfynd.xlsx
+++ b/artfynd/A 35188-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AZ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -782,6 +787,11 @@
           <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127475412</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -890,6 +900,11 @@
       <c r="AY3" t="inlineStr">
         <is>
           <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127475411</t>
         </is>
       </c>
     </row>
@@ -998,6 +1013,11 @@
           <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127475408</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1103,8 +1123,19 @@
           <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127503778</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>